--- a/Analysis/Sensitivity_alpha_sweep_qwen.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_qwen.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.009980000000000001</v>
+        <v>0.00546297435897436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007760000000000001</v>
+        <v>-0.0005034871794871783</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30012</v>
+        <v>0.3076657435897436</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6772799999999999</v>
+        <v>0.6646036923076923</v>
       </c>
       <c r="J2" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2082</v>
+        <v>0.14736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.22412</v>
+        <v>0.15898</v>
       </c>
       <c r="H3" t="n">
-        <v>0.46566</v>
+        <v>0.43898</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7805199999999999</v>
+        <v>0.73948</v>
       </c>
       <c r="J3" t="n">
         <v>195</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8895199999999999</v>
+        <v>0.8517999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.89724</v>
+        <v>0.8646200000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.96918</v>
+        <v>0.9599800000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -607,19 +607,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.00928</v>
+        <v>-0.002732102564102563</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005679999999999999</v>
+        <v>-0.006662358974358973</v>
       </c>
       <c r="H5" t="n">
-        <v>0.30014</v>
+        <v>0.2922995897435897</v>
       </c>
       <c r="I5" t="n">
-        <v>0.68138</v>
+        <v>0.6574143589743591</v>
       </c>
       <c r="J5" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6">
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.19112</v>
+        <v>0.16306</v>
       </c>
       <c r="G6" t="n">
-        <v>0.20562</v>
+        <v>0.17538</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45026</v>
+        <v>0.45128</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7702600000000001</v>
+        <v>0.76102</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8595200000000001</v>
+        <v>0.8119800000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8730800000000001</v>
+        <v>0.8323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8808</v>
+        <v>0.84512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9681599999999999</v>
+        <v>0.9641</v>
       </c>
       <c r="J7" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.01066</v>
+        <v>0.003407897435897436</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00776</v>
+        <v>-0.002556820512820513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.30014</v>
+        <v>0.3056124102564103</v>
       </c>
       <c r="I8" t="n">
-        <v>0.67728</v>
+        <v>0.6625503589743589</v>
       </c>
       <c r="J8" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.20752</v>
+        <v>0.1494</v>
       </c>
       <c r="G9" t="n">
-        <v>0.22202</v>
+        <v>0.16052</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46258</v>
+        <v>0.44308</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7794800000000001</v>
+        <v>0.7384600000000001</v>
       </c>
       <c r="J9" t="n">
         <v>195</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.87804</v>
+        <v>0.83794</v>
       </c>
       <c r="G10" t="n">
-        <v>0.88852</v>
+        <v>0.85334</v>
       </c>
       <c r="H10" t="n">
-        <v>0.89416</v>
+        <v>0.8636000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9702</v>
+        <v>0.9641</v>
       </c>
       <c r="J10" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.007940000000000001</v>
+        <v>0.008207282051282053</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0062</v>
+        <v>0.002573846153846156</v>
       </c>
       <c r="H11" t="n">
-        <v>0.29704</v>
+        <v>0.3066508717948718</v>
       </c>
       <c r="I11" t="n">
-        <v>0.67726</v>
+        <v>0.6646181538461539</v>
       </c>
       <c r="J11" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.21024</v>
+        <v>0.14598</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22614</v>
+        <v>0.15744</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4676999999999999</v>
+        <v>0.43692</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7825599999999999</v>
+        <v>0.73744</v>
       </c>
       <c r="J12" t="n">
         <v>195</v>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.87804</v>
+        <v>0.83866</v>
       </c>
       <c r="G13" t="n">
-        <v>0.88852</v>
+        <v>0.8574399999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.89416</v>
+        <v>0.8635999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9702</v>
+        <v>0.96204</v>
       </c>
       <c r="J13" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.01272</v>
+        <v>0.01093189743589744</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01032</v>
+        <v>0.004607384615384616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.30218</v>
+        <v>0.304626358974359</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6782999999999999</v>
+        <v>0.6584528205128205</v>
       </c>
       <c r="J14" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15">
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.21642</v>
+        <v>0.14328</v>
       </c>
       <c r="G15" t="n">
-        <v>0.23178</v>
+        <v>0.1564</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4697600000000001</v>
+        <v>0.43486</v>
       </c>
       <c r="I15" t="n">
-        <v>0.78154</v>
+        <v>0.73846</v>
       </c>
       <c r="J15" t="n">
         <v>195</v>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8732599999999999</v>
+        <v>0.83592</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8864600000000001</v>
+        <v>0.8538399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8911</v>
+        <v>0.85846</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9702</v>
+        <v>0.9672000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
